--- a/data/HNH_Projects_Fellowship.xlsx
+++ b/data/HNH_Projects_Fellowship.xlsx
@@ -6471,7 +6471,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -6520,7 +6520,7 @@
         <v>853</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>854</v>
